--- a/research/traditional_assets/database/data/austria/austria_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_drugs_pharmaceutical.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.2007751937984495</v>
+        <v>0.01484374999999996</v>
       </c>
       <c r="H2">
-        <v>-0.5387596899224806</v>
+        <v>-0.475</v>
       </c>
       <c r="I2">
-        <v>-0.610077519379845</v>
+        <v>-0.27421875</v>
       </c>
       <c r="J2">
-        <v>-0.610077519379845</v>
+        <v>-0.27421875</v>
       </c>
       <c r="K2">
-        <v>-8.49</v>
+        <v>-5.27</v>
       </c>
       <c r="L2">
-        <v>-0.6581395348837209</v>
+        <v>-0.41171875</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.06</v>
+        <v>9.32</v>
       </c>
       <c r="V2">
-        <v>0.02752542372881356</v>
+        <v>0.1026431718061674</v>
       </c>
       <c r="W2">
-        <v>-0.9496644295302015</v>
+        <v>7.853949329359164</v>
       </c>
       <c r="X2">
-        <v>0.06346304109061258</v>
+        <v>0.1171239802839329</v>
       </c>
       <c r="Y2">
-        <v>-1.013127470620814</v>
+        <v>7.736825349075231</v>
       </c>
       <c r="Z2">
-        <v>2.324324324324325</v>
+        <v>1.177661238384396</v>
       </c>
       <c r="AA2">
-        <v>-1.418018018018018</v>
+        <v>-0.3229367927132211</v>
       </c>
       <c r="AB2">
-        <v>0.05928596261035449</v>
+        <v>0.1028528976640406</v>
       </c>
       <c r="AC2">
-        <v>-1.477303980628373</v>
+        <v>-0.4257896903772617</v>
       </c>
       <c r="AD2">
-        <v>15.7</v>
+        <v>22.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.7</v>
+        <v>22.6</v>
       </c>
       <c r="AG2">
-        <v>11.64</v>
+        <v>13.28</v>
       </c>
       <c r="AH2">
-        <v>0.09620098039215687</v>
+        <v>0.199294532627866</v>
       </c>
       <c r="AI2">
-        <v>0.9154518950437318</v>
+        <v>1.182008368200837</v>
       </c>
       <c r="AJ2">
-        <v>0.07314314440115623</v>
+        <v>0.1275941583397387</v>
       </c>
       <c r="AK2">
-        <v>0.8892284186401834</v>
+        <v>1.355102040816327</v>
       </c>
       <c r="AL2">
-        <v>1.32</v>
+        <v>2.34</v>
       </c>
       <c r="AM2">
-        <v>1.257</v>
+        <v>2.25</v>
       </c>
       <c r="AN2">
-        <v>-2.093333333333333</v>
+        <v>-7.337662337662338</v>
       </c>
       <c r="AO2">
-        <v>-5.962121212121212</v>
+        <v>-1.5</v>
       </c>
       <c r="AP2">
-        <v>-1.552</v>
+        <v>-4.311688311688312</v>
       </c>
       <c r="AQ2">
-        <v>-6.260938743038981</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.2007751937984495</v>
+        <v>0.01484374999999996</v>
       </c>
       <c r="H3">
-        <v>-0.5387596899224806</v>
+        <v>-0.475</v>
       </c>
       <c r="I3">
-        <v>-0.610077519379845</v>
+        <v>-0.27421875</v>
       </c>
       <c r="J3">
-        <v>-0.610077519379845</v>
+        <v>-0.27421875</v>
       </c>
       <c r="K3">
-        <v>-8.49</v>
+        <v>-5.27</v>
       </c>
       <c r="L3">
-        <v>-0.6581395348837209</v>
+        <v>-0.41171875</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.06</v>
+        <v>9.32</v>
       </c>
       <c r="V3">
-        <v>0.02752542372881356</v>
+        <v>0.1026431718061674</v>
       </c>
       <c r="W3">
-        <v>-0.9496644295302015</v>
+        <v>7.853949329359164</v>
       </c>
       <c r="X3">
-        <v>0.06346304109061258</v>
+        <v>0.1171239802839329</v>
       </c>
       <c r="Y3">
-        <v>-1.013127470620814</v>
+        <v>7.736825349075231</v>
       </c>
       <c r="Z3">
-        <v>2.324324324324325</v>
+        <v>1.177661238384396</v>
       </c>
       <c r="AA3">
-        <v>-1.418018018018018</v>
+        <v>-0.3229367927132211</v>
       </c>
       <c r="AB3">
-        <v>0.05928596261035449</v>
+        <v>0.1028528976640406</v>
       </c>
       <c r="AC3">
-        <v>-1.477303980628373</v>
+        <v>-0.4257896903772617</v>
       </c>
       <c r="AD3">
-        <v>15.7</v>
+        <v>22.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.7</v>
+        <v>22.6</v>
       </c>
       <c r="AG3">
-        <v>11.64</v>
+        <v>13.28</v>
       </c>
       <c r="AH3">
-        <v>0.09620098039215687</v>
+        <v>0.199294532627866</v>
       </c>
       <c r="AI3">
-        <v>0.9154518950437318</v>
+        <v>1.182008368200837</v>
       </c>
       <c r="AJ3">
-        <v>0.07314314440115623</v>
+        <v>0.1275941583397387</v>
       </c>
       <c r="AK3">
-        <v>0.8892284186401834</v>
+        <v>1.355102040816327</v>
       </c>
       <c r="AL3">
-        <v>1.32</v>
+        <v>2.34</v>
       </c>
       <c r="AM3">
-        <v>1.257</v>
+        <v>2.25</v>
       </c>
       <c r="AN3">
-        <v>-2.093333333333333</v>
+        <v>-7.337662337662338</v>
       </c>
       <c r="AO3">
-        <v>-5.962121212121212</v>
+        <v>-1.5</v>
       </c>
       <c r="AP3">
-        <v>-1.552</v>
+        <v>-4.311688311688312</v>
       </c>
       <c r="AQ3">
-        <v>-6.260938743038981</v>
+        <v>-1.56</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_drugs_pharmaceutical.xlsx
@@ -587,32 +587,35 @@
           <t>Drugs (Pharmaceutical)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.149</v>
+      </c>
       <c r="G2">
-        <v>0.01484374999999996</v>
+        <v>0.2341666666666667</v>
       </c>
       <c r="H2">
-        <v>-0.475</v>
+        <v>-0.4075</v>
       </c>
       <c r="I2">
-        <v>-0.27421875</v>
+        <v>-0.4875</v>
       </c>
       <c r="J2">
-        <v>-0.27421875</v>
+        <v>-0.4875</v>
       </c>
       <c r="K2">
-        <v>-5.27</v>
+        <v>-6.58</v>
       </c>
       <c r="L2">
-        <v>-0.41171875</v>
+        <v>-0.5483333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.001775510204081633</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.01322188449848024</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,34 +627,37 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>9.32</v>
+        <v>2.93</v>
       </c>
       <c r="V2">
-        <v>0.1026431718061674</v>
+        <v>0.05979591836734694</v>
       </c>
       <c r="W2">
-        <v>7.853949329359164</v>
+        <v>1.890804597701149</v>
       </c>
       <c r="X2">
-        <v>0.1171239802839329</v>
+        <v>0.1007040527375863</v>
       </c>
       <c r="Y2">
-        <v>7.736825349075231</v>
+        <v>1.790100544963563</v>
       </c>
       <c r="Z2">
-        <v>1.177661238384396</v>
+        <v>1.224489795918367</v>
       </c>
       <c r="AA2">
-        <v>-0.3229367927132211</v>
+        <v>-0.596938775510204</v>
       </c>
       <c r="AB2">
-        <v>0.1028528976640406</v>
+        <v>0.08076722335929096</v>
       </c>
       <c r="AC2">
-        <v>-0.4257896903772617</v>
+        <v>-0.677705998869495</v>
       </c>
       <c r="AD2">
         <v>22.6</v>
@@ -663,37 +669,37 @@
         <v>22.6</v>
       </c>
       <c r="AG2">
-        <v>13.28</v>
+        <v>19.67</v>
       </c>
       <c r="AH2">
-        <v>0.199294532627866</v>
+        <v>0.3156424581005587</v>
       </c>
       <c r="AI2">
-        <v>1.182008368200837</v>
+        <v>1.745173745173745</v>
       </c>
       <c r="AJ2">
-        <v>0.1275941583397387</v>
+        <v>0.2864424057084607</v>
       </c>
       <c r="AK2">
-        <v>1.355102040816327</v>
+        <v>1.963073852295409</v>
       </c>
       <c r="AL2">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AM2">
-        <v>2.25</v>
+        <v>1.814</v>
       </c>
       <c r="AN2">
-        <v>-7.337662337662338</v>
+        <v>-4.16206261510129</v>
       </c>
       <c r="AO2">
-        <v>-1.5</v>
+        <v>-2.294117647058823</v>
       </c>
       <c r="AP2">
-        <v>-4.311688311688312</v>
+        <v>-3.622467771639043</v>
       </c>
       <c r="AQ2">
-        <v>-1.56</v>
+        <v>-3.224917309812569</v>
       </c>
     </row>
     <row r="3">
@@ -712,32 +718,35 @@
           <t>Drugs (Pharmaceutical)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.149</v>
+      </c>
       <c r="G3">
-        <v>0.01484374999999996</v>
+        <v>0.2341666666666667</v>
       </c>
       <c r="H3">
-        <v>-0.475</v>
+        <v>-0.4075</v>
       </c>
       <c r="I3">
-        <v>-0.27421875</v>
+        <v>-0.4875</v>
       </c>
       <c r="J3">
-        <v>-0.27421875</v>
+        <v>-0.4875</v>
       </c>
       <c r="K3">
-        <v>-5.27</v>
+        <v>-6.58</v>
       </c>
       <c r="L3">
-        <v>-0.41171875</v>
+        <v>-0.5483333333333333</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.001775510204081633</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.01322188449848024</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,34 +758,37 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>9.32</v>
+        <v>2.93</v>
       </c>
       <c r="V3">
-        <v>0.1026431718061674</v>
+        <v>0.05979591836734694</v>
       </c>
       <c r="W3">
-        <v>7.853949329359164</v>
+        <v>1.890804597701149</v>
       </c>
       <c r="X3">
-        <v>0.1171239802839329</v>
+        <v>0.1007040527375863</v>
       </c>
       <c r="Y3">
-        <v>7.736825349075231</v>
+        <v>1.790100544963563</v>
       </c>
       <c r="Z3">
-        <v>1.177661238384396</v>
+        <v>1.224489795918367</v>
       </c>
       <c r="AA3">
-        <v>-0.3229367927132211</v>
+        <v>-0.596938775510204</v>
       </c>
       <c r="AB3">
-        <v>0.1028528976640406</v>
+        <v>0.08076722335929096</v>
       </c>
       <c r="AC3">
-        <v>-0.4257896903772617</v>
+        <v>-0.677705998869495</v>
       </c>
       <c r="AD3">
         <v>22.6</v>
@@ -788,37 +800,37 @@
         <v>22.6</v>
       </c>
       <c r="AG3">
-        <v>13.28</v>
+        <v>19.67</v>
       </c>
       <c r="AH3">
-        <v>0.199294532627866</v>
+        <v>0.3156424581005587</v>
       </c>
       <c r="AI3">
-        <v>1.182008368200837</v>
+        <v>1.745173745173745</v>
       </c>
       <c r="AJ3">
-        <v>0.1275941583397387</v>
+        <v>0.2864424057084607</v>
       </c>
       <c r="AK3">
-        <v>1.355102040816327</v>
+        <v>1.963073852295409</v>
       </c>
       <c r="AL3">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AM3">
-        <v>2.25</v>
+        <v>1.814</v>
       </c>
       <c r="AN3">
-        <v>-7.337662337662338</v>
+        <v>-4.16206261510129</v>
       </c>
       <c r="AO3">
-        <v>-1.5</v>
+        <v>-2.294117647058823</v>
       </c>
       <c r="AP3">
-        <v>-4.311688311688312</v>
+        <v>-3.622467771639043</v>
       </c>
       <c r="AQ3">
-        <v>-1.56</v>
+        <v>-3.224917309812569</v>
       </c>
     </row>
   </sheetData>
